--- a/khurana_cv/data/research_projects_details.xlsx
+++ b/khurana_cv/data/research_projects_details.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\havis\University of Oregon Dropbox\Havi Khurana\Personal\Coding projects\khurana_cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F0C7EB-EEBB-4391-931A-01C2C2DC5F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEF4F45-4157-4360-B5CC-0FF6713FFF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
   <si>
     <t>type</t>
   </si>
@@ -93,43 +93,87 @@
     <t>Spanish Instructions as a DIBELS® Accommodation</t>
   </si>
   <si>
-    <t>Employed multi-level piecewise growth models to estimate shifts in average reading scores and examine demographic heterogeneity in a large urban district panel sample during the years impacted by COVID-19 school closures.
-Summarized findings in a executive report and presented results to district administration.</t>
-  </si>
-  <si>
-    <t>Performed regression and power analysis as outlined in the pre-analysis plan for an RCT design and drafted a technical report.</t>
-  </si>
-  <si>
     <t>Special education expenditures in Oregon</t>
   </si>
   <si>
-    <t>Wrangled Oregon administrative data on discipline, high-school graduation, and National Student Clearinghouse data on college outcomes for estimating principle effects using value-added-models on students' long-term outcomes.</t>
-  </si>
-  <si>
-    <t>Developed the research design and used several matching-on-observable estimators to identify the causal effect of the tutoring program on struggling readers.</t>
-  </si>
-  <si>
-    <t>Compiled Oregon administrative data on student membership, student state achievement, and special education expenditure for 2022.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summarized, visualized, and created R dashboards to describe changes in student reading outcomes across COVID-19 school closure phases for internal use.
-Conducted a comprehensive literature review on the early evidence of learning growth changes related to COVID-19 pandemic for internal purposes.
+    <t>Effects of administrative directions on the DIBELS8 nonsense-word fluency (NWF) subtest</t>
+  </si>
+  <si>
+    <t>Getting Down to Facts III, SCALE Initiative, Stanford University</t>
+  </si>
+  <si>
+    <t>Dr. Ilana Umansky</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Differences in California Reclassification Effects by Criterion and Threshold Level</t>
+  </si>
+  <si>
+    <t>Dr. Ilana Umansky and Dr. Karen Thomspon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National R&amp;D Center to Improve Education for Secondary English Learners  </t>
+  </si>
+  <si>
+    <t>Exploring Integrated English Language Development programs in Oregon</t>
+  </si>
+  <si>
+    <t>Compiled analysis-ready data file using administrative data; performed statistical analysis using multi-level regression models, variation decomposition analysis, and unsupervised machine learning clustering algorithm</t>
+  </si>
+  <si>
+    <t>Wrangled administrative data on discipline, high-school graduation, and college outcomes for estimating principle effects using value-added-models on students' long-term outcomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summarized, visualized, and created Shiny dashboards to describe changes in student reading outcomes across COVID-19 school closure phases for internal use; conducted comprehensive literature review on the early evidence of learning growth changes related to COVID-19 pandemic for internal purposes
 </t>
   </si>
   <si>
-    <t>Automated test form generation and quality control checks for alternative DIBELS8 subtests using R.</t>
-  </si>
-  <si>
-    <t>Compiled analysis-ready data file using Oregon administrative data.
-Performed statistical analysis using multi-level regression models, variation decomposition analysis, and unsupervised machine learning clustering algorithm.
-Shared research findings at two national-level policy conferences and co-drafted a working paper.</t>
+    <t>Automated test form generation and quality control checks for alternative DIBELS8 subtests using R</t>
+  </si>
+  <si>
+    <t>Employed multi-level piecewise growth models to estimate shifts in average reading scores and examine demographic heterogeneity in a large urban district panel sample during the years impacted by COVID-19 school closures; summarized findings in a executive report and presented results to district administration</t>
+  </si>
+  <si>
+    <t>Performed regression and power analysis as outlined in the pre-analysis plan for an RCT design; drafted a technical report.</t>
+  </si>
+  <si>
+    <t>Developed the research design using several matching-on-observable estimators to identify the causal effect of the tutoring program on struggling readers; reported findings to district leaders</t>
+  </si>
+  <si>
+    <t>2024/2025</t>
+  </si>
+  <si>
+    <t>Compiled administrative data on student membership, student state achievement, and special education expenditure for 2022</t>
+  </si>
+  <si>
+    <t>Co-developed the research question and methods; compiled data on district reclassification crtierias; used descriptive statistics and fuzzy regression discontinuity design to estimate the effect of an additional academic criterion on students's outcomes</t>
+  </si>
+  <si>
+    <t>Co-developed the research question and methods; led quantative analysis for the project</t>
+  </si>
+  <si>
+    <t>iMentor</t>
+  </si>
+  <si>
+    <t>Dr. Kallen Tsikalas</t>
+  </si>
+  <si>
+    <t>iMentor College: Mapping Text-Prompt Response Rate and Pair Connection</t>
+  </si>
+  <si>
+    <t>Refined stakeholders' research questions; developed the researc plan; conducted literature review on pair/small-group mentoring program models and their effects on student outcomes; harmonized all primary data files into a meta-dataset; used descriptive statistics to highlight usage trends</t>
+  </si>
+  <si>
+    <t>Co-developed the analytical plan; performed multi-level linear regression for a repeated measures RCT design; drafted a technical report</t>
+  </si>
+  <si>
+    <t>order</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +192,11 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Times Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -196,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -212,6 +261,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,16 +542,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="5" width="27.1796875" customWidth="1"/>
-    <col min="6" max="6" width="22.26953125" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="6" width="27.1796875" customWidth="1"/>
+    <col min="7" max="7" width="22.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -509,206 +560,335 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="145" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="116">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2">
         <v>2022</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2">
+      <c r="G2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2">
         <v>0.25</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="232" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="159.5">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2">
         <v>2023</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.33</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="217.5">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="4">
         <v>2022</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="4">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4">
+      <c r="G4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4">
         <v>0.49</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="72.5">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5">
         <v>2023</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5">
+      <c r="G5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5">
         <v>0.25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="217.5">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6">
         <v>2023</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6">
+      <c r="G6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6">
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="87">
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B7">
         <v>2024</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7">
+      <c r="G7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7">
         <v>0.4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="130.5">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B8">
-        <v>2024</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8">
+      <c r="G8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8">
         <v>0.4</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="87">
       <c r="A9" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B9">
         <v>2024</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="203">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>2025</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="101.5">
+      <c r="A11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>2025</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="159.5">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>2025</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12">
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="31">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>2025</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>27</v>
+      </c>
+      <c r="F13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>